--- a/tests/fixtures/18_billing_statement/18_billing_statement_pattern-from-claude.xlsx
+++ b/tests/fixtures/18_billing_statement/18_billing_statement_pattern-from-claude.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>City, ST ZIP Code</t>
+          <t>City, ST  ZIP Code</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>company.name</t>
+          <t>company.phone</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>company.phone</t>
+          <t>company.fax</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>company.fax</t>
+          <t>company.email</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>company.email</t>
+          <t>stmt.number</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>stmt.number</t>
+          <t>stmt.bill_to</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1327,19 +1327,15 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>stmt.bill_to</t>
+          <t>stmt.date</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -1354,15 +1350,19 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>stmt.date</t>
+          <t>stmt.customer_id</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
@@ -1377,19 +1377,15 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>stmt.customer_id</t>
+          <t>line.date</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
@@ -1404,15 +1400,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>line.date</t>
+          <t>line.type</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
@@ -1427,17 +1427,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>line.type</t>
+          <t>line.invoice_num</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\d+</t>
         </is>
       </c>
       <c r="E37" s="3" t="n"/>
@@ -1454,17 +1454,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>line.invoice_num</t>
+          <t>line.description</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E38" s="3" t="n"/>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>line.description</t>
+          <t>line.amount</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>line.amount</t>
+          <t>line.payment</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>line.payment</t>
+          <t>line.balance</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>line.balance</t>
+          <t>remittance.customer_name</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1589,19 +1589,15 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>remittance.customer_name</t>
+          <t>remittance.date</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
@@ -1609,42 +1605,38 @@
       <c r="I43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>remittance.date</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>START:</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>START:</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -1654,7 +1646,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>street_address</t>
         </is>
       </c>
       <c r="C46" s="5" t="n"/>
@@ -1673,7 +1665,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>street_address</t>
+          <t>phone_label</t>
         </is>
       </c>
       <c r="C47" s="5" t="n"/>
@@ -1692,7 +1684,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>phone_label</t>
+          <t>company.phone</t>
         </is>
       </c>
       <c r="C48" s="5" t="n"/>
@@ -1711,7 +1703,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>company.phone</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C49" s="5" t="n"/>
@@ -1730,7 +1722,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>address_2</t>
+          <t>fax_label</t>
         </is>
       </c>
       <c r="C50" s="5" t="n"/>
@@ -1749,7 +1741,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>fax_label</t>
+          <t>company.fax</t>
         </is>
       </c>
       <c r="C51" s="5" t="n"/>
@@ -1768,7 +1760,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>company.fax</t>
+          <t>city_zip</t>
         </is>
       </c>
       <c r="C52" s="5" t="n"/>
@@ -1787,7 +1779,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>city_zip</t>
+          <t>email_label</t>
         </is>
       </c>
       <c r="C53" s="5" t="n"/>
@@ -1806,7 +1798,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>email_label</t>
+          <t>company.email</t>
         </is>
       </c>
       <c r="C54" s="5" t="n"/>
@@ -1825,7 +1817,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>company.email</t>
+          <t>statement_label</t>
         </is>
       </c>
       <c r="C55" s="5" t="n"/>
@@ -1844,7 +1836,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>statement_label</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C56" s="5" t="n"/>
@@ -1863,7 +1855,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>statement_num_label</t>
         </is>
       </c>
       <c r="C57" s="5" t="n"/>
@@ -1882,7 +1874,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>statement_num_label</t>
+          <t>stmt.number</t>
         </is>
       </c>
       <c r="C58" s="5" t="n"/>
@@ -1901,7 +1893,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>stmt.number</t>
+          <t>bill_to_label</t>
         </is>
       </c>
       <c r="C59" s="5" t="n"/>
@@ -1920,7 +1912,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>bill_to_label</t>
+          <t>stmt.bill_to</t>
         </is>
       </c>
       <c r="C60" s="5" t="n"/>
@@ -1939,7 +1931,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>stmt.bill_to</t>
+          <t>date_label</t>
         </is>
       </c>
       <c r="C61" s="5" t="n"/>
@@ -1958,7 +1950,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>date_label</t>
+          <t>stmt.date</t>
         </is>
       </c>
       <c r="C62" s="5" t="n"/>
@@ -1977,7 +1969,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>stmt.date</t>
+          <t>company_name_2</t>
         </is>
       </c>
       <c r="C63" s="5" t="n"/>
@@ -1996,7 +1988,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>company_name_2</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C64" s="5" t="n"/>
@@ -2015,7 +2007,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>customer_id_label</t>
         </is>
       </c>
       <c r="C65" s="5" t="n"/>
@@ -2034,7 +2026,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>customer_id_label</t>
+          <t>stmt.customer_id</t>
         </is>
       </c>
       <c r="C66" s="5" t="n"/>
@@ -2053,7 +2045,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>stmt.customer_id</t>
+          <t>street_address_2</t>
         </is>
       </c>
       <c r="C67" s="5" t="n"/>
@@ -2072,7 +2064,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>street_address_2</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C68" s="5" t="n"/>
@@ -2091,7 +2083,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>address_2_2</t>
         </is>
       </c>
       <c r="C69" s="5" t="n"/>
@@ -2110,7 +2102,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>address_2_2</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C70" s="5" t="n"/>
@@ -2129,7 +2121,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>city_zip_2</t>
         </is>
       </c>
       <c r="C71" s="5" t="n"/>
@@ -2148,7 +2140,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>city_zip_2</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C72" s="5" t="n"/>
@@ -2160,200 +2152,181 @@
       <c r="I72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="6" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>col_date</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>col_type</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>col_invoice</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>col_description</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>col_amount</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>col_payment</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>col_balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n"/>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>DATA:*</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>line.date</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>line.type</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>line.invoice_num</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>line.description</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>line.amount</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>line.payment</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>line.balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
-      <c r="G74" s="6" t="n"/>
-      <c r="H74" s="6" t="n"/>
-      <c r="I74" s="6" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>col_date</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>col_type</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>col_invoice</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>col_description</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>col_amount</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>col_payment</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>col_balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n"/>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>remittance_customer_name</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>remittance_enter_customer</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n"/>
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>line.date</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>line.type</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>line.invoice_num</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>line.description</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>line.amount</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>line.payment</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>line.balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="D77" s="6" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
-      <c r="I77" s="6" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>remittance_customer_name</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>remittance_enter_customer</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n"/>
-      <c r="G78" s="2" t="n"/>
-      <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>remittance.customer_name</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>remittance.date</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n"/>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>DATA:*</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>remittance.customer_name</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>remittance.date</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n"/>
-      <c r="G79" s="3" t="n"/>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n"/>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
